--- a/output/pdf_financials_xlsx/KLDC.xlsx
+++ b/output/pdf_financials_xlsx/KLDC.xlsx
@@ -5876,49 +5876,49 @@
         <v>3.005628</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.033628</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.154847</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>3.164717</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.205553</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.396198</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.397698</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>4.314928</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>4.317178</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>4.600708</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>4.648108</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>4.891971</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.98469</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>7.098997</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>7.258893</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>9.681751</v>
       </c>
     </row>
     <row r="93">
@@ -9869,7 +9869,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -10724,7 +10728,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -12159,7 +12167,11 @@
           <t>Reserves 9,10</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -13450,7 +13462,11 @@
           <t>Reserves 8,9</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -14549,7 +14565,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -15044,7 +15064,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -15709,7 +15733,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -16309,7 +16337,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E82" s="5" t="n">
         <v>2.984858</v>
       </c>

--- a/output/pdf_financials_xlsx/KLDC.xlsx
+++ b/output/pdf_financials_xlsx/KLDC.xlsx
@@ -1041,13 +1041,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.003913</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.002012</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.004067</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1083,13 +1083,13 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>7.7e-05</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.006959</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.09540700000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.319383</v>
+        <v>-1.323296</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.540263</v>
+        <v>-3.542275</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.641854</v>
+        <v>-0.645921</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-1.052155</v>
@@ -2025,13 +2025,13 @@
         <v>-1.044306</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-3.795575</v>
+        <v>-3.795652</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-2.786044</v>
+        <v>-2.793003</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-7.529527</v>
+        <v>-7.624934</v>
       </c>
     </row>
     <row r="28">
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.319383</v>
+        <v>-1.323296</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.540263</v>
+        <v>-3.542275</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.641854</v>
+        <v>-0.645921</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-1.052155</v>
@@ -2141,13 +2141,13 @@
         <v>-1.037348</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-3.793533</v>
+        <v>-3.79361</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-2.78022</v>
+        <v>-2.787179</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-7.506639</v>
+        <v>-7.602046</v>
       </c>
     </row>
     <row r="30">
@@ -2415,37 +2415,37 @@
         <v>0.271187</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.163082</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.021807</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.183174</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.000544</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.682272</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.968507</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.914488</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.070378</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.409534</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.251707</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.070634</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>3.246345</v>
@@ -2531,37 +2531,37 @@
         <v>0.271187</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.163082</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.021807</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.183174</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.04</v>
+        <v>0.040544</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.682272</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.968507</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.914488</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.070378</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.409534</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.251707</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.070634</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>3.246345</v>
@@ -3239,25 +3239,25 @@
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.6879729999999999</v>
+        <v>0.005701</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.184624</v>
+        <v>0.216117</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.9205759999999999</v>
+        <v>0.006088</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.085311</v>
+        <v>0.014933</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.424763</v>
+        <v>0.015229</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.6186430000000001</v>
+        <v>0.366936</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.080899</v>
+        <v>0.010265</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>0.034808</v>
@@ -7735,19 +7735,19 @@
         <v>0</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.007776</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.010142</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.011793</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.014421</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.001084</v>
       </c>
       <c r="Q124" s="3" t="n">
         <v>0</v>
@@ -7793,19 +7793,19 @@
         <v>0</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.007776</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.010142</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.011793</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.014421</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.001084</v>
       </c>
       <c r="Q125" s="3" t="n">
         <v>0</v>
@@ -10831,7 +10831,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -20337,7 +20337,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -21438,7 +21442,11 @@
           <t>Interest expense on lease payments</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -22368,7 +22376,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -23961,7 +23973,11 @@
           <t>Lease payments 6</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -24767,7 +24783,11 @@
           <t>Lease payments 4</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -34257,7 +34277,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -37883,7 +37903,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -44223,7 +44243,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E364" s="5" t="n">

--- a/output/pdf_financials_xlsx/KLDC.xlsx
+++ b/output/pdf_financials_xlsx/KLDC.xlsx
@@ -7476,19 +7476,19 @@
         <v>0</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0</v>
+        <v>0.906686</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>0</v>
+        <v>0.929765</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>0</v>
+        <v>0.304968</v>
       </c>
       <c r="F120" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>0</v>
+        <v>0.100442</v>
       </c>
       <c r="H120" s="3" t="n">
         <v>0</v>
@@ -27205,7 +27205,11 @@
           <t>Issuance of common shares, net of issue costs</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -29219,7 +29223,11 @@
           <t>Issuance of common shares, net of issue costs 10</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/KLDC.xlsx
+++ b/output/pdf_financials_xlsx/KLDC.xlsx
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.114225</v>
+        <v>0.202733</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.152507</v>
+        <v>0.23873</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.18929</v>
+        <v>0.23129</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.133753</v>
+        <v>0.226698</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0.201525</v>
@@ -925,16 +925,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.114225</v>
+        <v>0.202733</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.152507</v>
+        <v>0.23873</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.18929</v>
+        <v>0.23129</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.133753</v>
+        <v>0.226698</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0.08587</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.114225</v>
+        <v>-0.202733</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-0.579184</v>
@@ -4583,7 +4583,7 @@
         <v>0</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.002243</v>
       </c>
       <c r="P70" s="3" t="n">
         <v>0</v>
@@ -4641,7 +4641,7 @@
         <v>0.002414</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0.002313</v>
+        <v>0.004556</v>
       </c>
       <c r="P71" s="3" t="n">
         <v>0</v>
@@ -4873,7 +4873,7 @@
         <v>0.210511</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.231449</v>
+        <v>0.229206</v>
       </c>
       <c r="P75" s="3" t="n">
         <v>0.166117</v>
@@ -5187,7 +5187,7 @@
         <v>0.0004376349366834342</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.0004701512878954032</v>
+        <v>0.0009260740456772405</v>
       </c>
       <c r="P80" s="1" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>-0.075111</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0.004462</v>
+        <v>0.109234</v>
       </c>
       <c r="L101" s="3" t="n">
         <v>-0.09621499999999999</v>
@@ -6688,7 +6688,7 @@
         <v>-0.611652</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0.339287</v>
+        <v>0.444059</v>
       </c>
       <c r="L106" s="3" t="n">
         <v>-0.281357</v>
@@ -7183,7 +7183,7 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.187843</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -7204,7 +7204,7 @@
         <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.074642</v>
       </c>
       <c r="J115" s="3" t="n">
         <v>0</v>
@@ -11017,7 +11017,11 @@
           <t>Lease liabilities</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -18933,7 +18937,11 @@
           <t>Shares issued in private placement</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -24379,7 +24387,11 @@
           <t>Provision for GST receivable</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -26498,7 +26510,11 @@
           <t>Proceeds from sale of marketable securities 9</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -27003,7 +27019,11 @@
           <t>Proceeds from sale of marketable securities 8</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -31257,7 +31277,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E232" s="5" t="n">
         <v>0.187843</v>
       </c>
@@ -42350,7 +42374,11 @@
           <t>Directors’ fees 13</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
           <t>-</t>
@@ -44649,7 +44677,11 @@
           <t>Directors’ fees 9</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr"/>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E368" s="5" t="n">
         <v>0.088508</v>
       </c>
